--- a/Configs/GameConfig/Datas/局内.xlsx
+++ b/Configs/GameConfig/Datas/局内.xlsx
@@ -4,10 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28240" windowHeight="11090"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="局内常量" sheetId="1" r:id="rId1"/>
+    <sheet name="基础建筑表" sheetId="1" r:id="rId1"/>
+    <sheet name="基础单位表" sheetId="3" r:id="rId2"/>
+    <sheet name="子弹表" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,49 +30,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="83">
   <si>
     <t>##var</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>i</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>d</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>d</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>esc</t>
-    </r>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>bulletId</t>
+  </si>
+  <si>
+    <t>attack_interals</t>
+  </si>
+  <si>
+    <t>prefab_path</t>
   </si>
   <si>
     <t>##type</t>
@@ -81,6 +62,12 @@
     <t>string</t>
   </si>
   <si>
+    <t>int#ref=battle.TbBullet</t>
+  </si>
+  <si>
+    <t>(list#sep=|),float</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -90,57 +77,208 @@
     <t>##</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这是i</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>d</t>
-    </r>
+    <t>这是id</t>
+  </si>
+  <si>
+    <t>塔名称</t>
   </si>
   <si>
     <t>描述</t>
   </si>
   <si>
-    <t>奖励1</t>
-  </si>
-  <si>
-    <t>奖励2</t>
-  </si>
-  <si>
-    <t>奖励3</t>
-  </si>
-  <si>
-    <t>奖励4</t>
-  </si>
-  <si>
-    <t>奖励5</t>
-  </si>
-  <si>
-    <t>奖励6</t>
-  </si>
-  <si>
-    <t>奖励7</t>
-  </si>
-  <si>
-    <t>奖励8</t>
-  </si>
-  <si>
-    <t>奖励9</t>
-  </si>
-  <si>
-    <t>奖励10</t>
+    <t>子弹</t>
+  </si>
+  <si>
+    <t>攻击间隔等级配置</t>
+  </si>
+  <si>
+    <t>预制体路径</t>
+  </si>
+  <si>
+    <t>箭塔</t>
+  </si>
+  <si>
+    <t>基础单体攻击塔</t>
+  </si>
+  <si>
+    <t>Towers/ArrowTower.prefab</t>
+  </si>
+  <si>
+    <t>兵营</t>
+  </si>
+  <si>
+    <t>持续生成士兵</t>
+  </si>
+  <si>
+    <t>Towers/Barracks.prefab</t>
+  </si>
+  <si>
+    <t>鼓舞战旗</t>
+  </si>
+  <si>
+    <t>增加周围友军攻击力</t>
+  </si>
+  <si>
+    <t>Towers/BannerTower.prefab</t>
+  </si>
+  <si>
+    <t>unit_type</t>
+  </si>
+  <si>
+    <t>max_hp</t>
+  </si>
+  <si>
+    <t>attack</t>
+  </si>
+  <si>
+    <t>attack_range</t>
+  </si>
+  <si>
+    <t>attack_interval</t>
+  </si>
+  <si>
+    <t>defense</t>
+  </si>
+  <si>
+    <t>move_speed</t>
+  </si>
+  <si>
+    <t>EUnitType</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>单位id</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>单位类型</t>
+  </si>
+  <si>
+    <t>最大生命</t>
+  </si>
+  <si>
+    <t>攻击力</t>
+  </si>
+  <si>
+    <t>攻击距离</t>
+  </si>
+  <si>
+    <t>攻击间隔</t>
+  </si>
+  <si>
+    <t>防御力</t>
+  </si>
+  <si>
+    <t>移动速度</t>
+  </si>
+  <si>
+    <t>民兵</t>
+  </si>
+  <si>
+    <t>HERO</t>
+  </si>
+  <si>
+    <t>骑士</t>
+  </si>
+  <si>
+    <t>史莱姆</t>
+  </si>
+  <si>
+    <t>ENEMY</t>
+  </si>
+  <si>
+    <t>兽人战士</t>
+  </si>
+  <si>
+    <t>bullet_type</t>
+  </si>
+  <si>
+    <t>spawn_unit_id</t>
+  </si>
+  <si>
+    <t>damage</t>
+  </si>
+  <si>
+    <t>debuff_value</t>
+  </si>
+  <si>
+    <t>debuff_duration</t>
+  </si>
+  <si>
+    <t>speed</t>
+  </si>
+  <si>
+    <t>aoe_radius</t>
+  </si>
+  <si>
+    <t>EBulletType</t>
+  </si>
+  <si>
+    <t>int#ref=battle.TbUnit</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>子弹id</t>
+  </si>
+  <si>
+    <t>效果名</t>
+  </si>
+  <si>
+    <t>子弹类型</t>
+  </si>
+  <si>
+    <t>生成单位id</t>
+  </si>
+  <si>
+    <t>伤害</t>
+  </si>
+  <si>
+    <t>减益数值</t>
+  </si>
+  <si>
+    <t>持续时间</t>
+  </si>
+  <si>
+    <t>飞行速度</t>
+  </si>
+  <si>
+    <t>溅射半径</t>
+  </si>
+  <si>
+    <t>普通箭矢</t>
+  </si>
+  <si>
+    <t>PROJECTILE</t>
+  </si>
+  <si>
+    <t>强化箭矢</t>
+  </si>
+  <si>
+    <t>召唤士兵</t>
+  </si>
+  <si>
+    <t>SPAWN_UNIT</t>
+  </si>
+  <si>
+    <t>召唤骑士</t>
+  </si>
+  <si>
+    <t>攻击光环</t>
+  </si>
+  <si>
+    <t>INSTANT_AURA</t>
+  </si>
+  <si>
+    <t>狂热光环</t>
   </si>
 </sst>
 </file>
@@ -153,7 +291,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,6 +315,12 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -696,137 +840,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -865,10 +1009,16 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1222,25 +1372,24 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.29090909090909" style="1" customWidth="1"/>
     <col min="2" max="2" width="6.71818181818182" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.4363636363636" style="1" customWidth="1"/>
     <col min="4" max="4" width="33.8181818181818" style="2" customWidth="1"/>
-    <col min="5" max="5" width="32.5727272727273" style="2" customWidth="1"/>
-    <col min="6" max="6" width="48.1454545454545" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1454545454545" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.4363636363636" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.8636363636364" style="1" customWidth="1"/>
-    <col min="10" max="10" width="28.0090909090909" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.0090909090909" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.14545454545455" style="3" customWidth="1"/>
-    <col min="13" max="34" width="12.4363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="60.4545454545455" style="2" customWidth="1"/>
+    <col min="6" max="6" width="107.454545454545" style="1" customWidth="1"/>
+    <col min="7" max="7" width="48.3636363636364" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.8636363636364" style="1" customWidth="1"/>
+    <col min="9" max="9" width="28.0090909090909" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.0090909090909" style="3" customWidth="1"/>
+    <col min="11" max="11" width="5.14545454545455" style="3" customWidth="1"/>
+    <col min="12" max="33" width="12.4363636363636" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.75" customHeight="1" spans="1:13">
+    <row r="1" ht="21.75" customHeight="1" spans="1:12">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1250,214 +1399,764 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="8"/>
-    </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:13">
+      <c r="J1" s="6"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="8"/>
+    </row>
+    <row r="2" ht="21.75" customHeight="1" spans="1:12">
       <c r="A2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="9"/>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="8"/>
-    </row>
-    <row r="3" ht="21.75" customHeight="1" spans="1:13">
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="8"/>
+    </row>
+    <row r="3" ht="21.75" customHeight="1" spans="1:12">
       <c r="A3" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="10"/>
+        <v>7</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="C3" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="8"/>
-    </row>
-    <row r="4" ht="22.5" customHeight="1" spans="1:13">
+        <v>9</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="8"/>
+    </row>
+    <row r="4" ht="22.5" customHeight="1" spans="1:12">
       <c r="A4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="E4" s="5"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="8"/>
-    </row>
-    <row r="5" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B5" s="15">
+      <c r="G4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="15"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="8"/>
+    </row>
+    <row r="5" ht="20.25" customHeight="1" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+    </row>
+    <row r="6" ht="20.25" customHeight="1" spans="1:12">
+      <c r="B6" s="16">
+        <v>10001</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="16">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="1"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-    </row>
-    <row r="6" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B6" s="15">
+      <c r="G6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+    </row>
+    <row r="7" ht="20.25" customHeight="1" spans="1:12">
+      <c r="B7" s="16">
+        <v>10002</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="16">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="1"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-    </row>
-    <row r="7" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B7" s="15">
+      <c r="G7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+    </row>
+    <row r="8" ht="20.25" customHeight="1" spans="1:12">
+      <c r="B8" s="16">
+        <v>10003</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="16">
         <v>3</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="1"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-    </row>
-    <row r="8" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B8" s="15">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="1"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-    </row>
-    <row r="9" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B9" s="15">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="1"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-    </row>
-    <row r="10" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B10" s="15">
-        <v>6</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="1"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-    </row>
-    <row r="11" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B11" s="15">
-        <v>7</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="1"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-    </row>
-    <row r="12" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B12" s="15">
-        <v>8</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="1"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-    </row>
-    <row r="13" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B13" s="15">
-        <v>9</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="1"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-    </row>
-    <row r="14" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B14" s="15">
-        <v>10</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="1"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
+      <c r="G8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+    </row>
+    <row r="9" ht="20.25" customHeight="1" spans="1:12">
+      <c r="B9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+    </row>
+    <row r="10" ht="20.25" customHeight="1" spans="1:12">
+      <c r="B10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+    </row>
+    <row r="11" ht="20.25" customHeight="1" spans="1:12">
+      <c r="B11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+    </row>
+    <row r="12" ht="20.25" customHeight="1" spans="1:12">
+      <c r="B12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+    </row>
+    <row r="13" ht="20.25" customHeight="1" spans="1:12">
+      <c r="B13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+    </row>
+    <row r="14" ht="20.25" customHeight="1" spans="1:12">
+      <c r="B14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="J2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="53.4545454545455" customWidth="1"/>
+    <col min="3" max="3" width="38.1818181818182" customWidth="1"/>
+    <col min="4" max="4" width="25.1818181818182" customWidth="1"/>
+    <col min="5" max="5" width="25.4545454545455" customWidth="1"/>
+    <col min="6" max="6" width="24.6363636363636" customWidth="1"/>
+    <col min="7" max="7" width="23.5454545454545" customWidth="1"/>
+    <col min="8" max="8" width="29.1818181818182" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="B6">
+        <v>30001</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>1.2</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7">
+        <v>30002</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7">
+        <v>250</v>
+      </c>
+      <c r="F7">
+        <v>15</v>
+      </c>
+      <c r="G7">
+        <v>1.5</v>
+      </c>
+      <c r="H7">
+        <v>1.5</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8">
+        <v>40001</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="B9">
+        <v>40002</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9">
+        <v>120</v>
+      </c>
+      <c r="F9">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>3</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="49.3636363636364" customWidth="1"/>
+    <col min="3" max="3" width="31.6363636363636" customWidth="1"/>
+    <col min="4" max="4" width="28.1818181818182" customWidth="1"/>
+    <col min="5" max="5" width="36.1818181818182" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" t="s">
+        <v>64</v>
+      </c>
+      <c r="K4" t="s">
+        <v>64</v>
+      </c>
+      <c r="L4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="B6">
+        <v>20001</v>
+      </c>
+      <c r="C6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="B7">
+        <v>20002</v>
+      </c>
+      <c r="C7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7">
+        <v>18</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="B8">
+        <v>20003</v>
+      </c>
+      <c r="C8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8">
+        <v>30001</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="B9">
+        <v>20004</v>
+      </c>
+      <c r="C9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9">
+        <v>30002</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="B10">
+        <v>20005</v>
+      </c>
+      <c r="C10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0.15</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="B11">
+        <v>20006</v>
+      </c>
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0.25</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Configs/GameConfig/Datas/局内.xlsx
+++ b/Configs/GameConfig/Datas/局内.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="75">
   <si>
     <t>##var</t>
   </si>
@@ -47,10 +47,13 @@
     <t>bulletId</t>
   </si>
   <si>
+    <t>attack_range</t>
+  </si>
+  <si>
     <t>attack_interals</t>
   </si>
   <si>
-    <t>prefab_path</t>
+    <t>modelId</t>
   </si>
   <si>
     <t>##type</t>
@@ -65,9 +68,15 @@
     <t>int#ref=battle.TbBullet</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>(list#sep=|),float</t>
   </si>
   <si>
+    <t>int#ref=res.TbModel</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -89,169 +98,136 @@
     <t>子弹</t>
   </si>
   <si>
+    <t>攻击距离</t>
+  </si>
+  <si>
     <t>攻击间隔等级配置</t>
   </si>
   <si>
+    <t>模型</t>
+  </si>
+  <si>
+    <t>箭塔</t>
+  </si>
+  <si>
+    <t>基础单体攻击塔</t>
+  </si>
+  <si>
+    <t>兵营</t>
+  </si>
+  <si>
+    <t>持续生成士兵</t>
+  </si>
+  <si>
+    <t>鼓舞战旗</t>
+  </si>
+  <si>
+    <t>增加周围友军攻击力</t>
+  </si>
+  <si>
+    <t>unit_type</t>
+  </si>
+  <si>
+    <t>max_hp</t>
+  </si>
+  <si>
+    <t>attack</t>
+  </si>
+  <si>
+    <t>attack_interval</t>
+  </si>
+  <si>
+    <t>defense</t>
+  </si>
+  <si>
+    <t>move_speed</t>
+  </si>
+  <si>
+    <t>EUnitType</t>
+  </si>
+  <si>
+    <t>单位id</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>单位类型</t>
+  </si>
+  <si>
+    <t>最大生命</t>
+  </si>
+  <si>
+    <t>攻击力</t>
+  </si>
+  <si>
+    <t>攻击间隔</t>
+  </si>
+  <si>
+    <t>防御力</t>
+  </si>
+  <si>
+    <t>移动速度</t>
+  </si>
+  <si>
+    <t>民兵</t>
+  </si>
+  <si>
+    <t>HERO</t>
+  </si>
+  <si>
+    <t>骑士</t>
+  </si>
+  <si>
+    <t>史莱姆</t>
+  </si>
+  <si>
+    <t>ENEMY</t>
+  </si>
+  <si>
+    <t>兽人战士</t>
+  </si>
+  <si>
+    <t>bullet_type</t>
+  </si>
+  <si>
+    <t>debuff_duration</t>
+  </si>
+  <si>
+    <t>speed</t>
+  </si>
+  <si>
+    <t>buffs</t>
+  </si>
+  <si>
+    <t>EBulletType</t>
+  </si>
+  <si>
+    <t>int#ref=battle.TbBuff</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>子弹id</t>
+  </si>
+  <si>
+    <t>效果名</t>
+  </si>
+  <si>
+    <t>子弹类型</t>
+  </si>
+  <si>
+    <t>持续时间</t>
+  </si>
+  <si>
+    <t>飞行速度</t>
+  </si>
+  <si>
+    <t>施加buff</t>
+  </si>
+  <si>
     <t>预制体路径</t>
-  </si>
-  <si>
-    <t>箭塔</t>
-  </si>
-  <si>
-    <t>基础单体攻击塔</t>
-  </si>
-  <si>
-    <t>Towers/ArrowTower.prefab</t>
-  </si>
-  <si>
-    <t>兵营</t>
-  </si>
-  <si>
-    <t>持续生成士兵</t>
-  </si>
-  <si>
-    <t>Towers/Barracks.prefab</t>
-  </si>
-  <si>
-    <t>鼓舞战旗</t>
-  </si>
-  <si>
-    <t>增加周围友军攻击力</t>
-  </si>
-  <si>
-    <t>Towers/BannerTower.prefab</t>
-  </si>
-  <si>
-    <t>unit_type</t>
-  </si>
-  <si>
-    <t>max_hp</t>
-  </si>
-  <si>
-    <t>attack</t>
-  </si>
-  <si>
-    <t>attack_range</t>
-  </si>
-  <si>
-    <t>attack_interval</t>
-  </si>
-  <si>
-    <t>defense</t>
-  </si>
-  <si>
-    <t>move_speed</t>
-  </si>
-  <si>
-    <t>EUnitType</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>单位id</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>单位类型</t>
-  </si>
-  <si>
-    <t>最大生命</t>
-  </si>
-  <si>
-    <t>攻击力</t>
-  </si>
-  <si>
-    <t>攻击距离</t>
-  </si>
-  <si>
-    <t>攻击间隔</t>
-  </si>
-  <si>
-    <t>防御力</t>
-  </si>
-  <si>
-    <t>移动速度</t>
-  </si>
-  <si>
-    <t>民兵</t>
-  </si>
-  <si>
-    <t>HERO</t>
-  </si>
-  <si>
-    <t>骑士</t>
-  </si>
-  <si>
-    <t>史莱姆</t>
-  </si>
-  <si>
-    <t>ENEMY</t>
-  </si>
-  <si>
-    <t>兽人战士</t>
-  </si>
-  <si>
-    <t>bullet_type</t>
-  </si>
-  <si>
-    <t>spawn_unit_id</t>
-  </si>
-  <si>
-    <t>damage</t>
-  </si>
-  <si>
-    <t>debuff_value</t>
-  </si>
-  <si>
-    <t>debuff_duration</t>
-  </si>
-  <si>
-    <t>speed</t>
-  </si>
-  <si>
-    <t>aoe_radius</t>
-  </si>
-  <si>
-    <t>EBulletType</t>
-  </si>
-  <si>
-    <t>int#ref=battle.TbUnit</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>子弹id</t>
-  </si>
-  <si>
-    <t>效果名</t>
-  </si>
-  <si>
-    <t>子弹类型</t>
-  </si>
-  <si>
-    <t>生成单位id</t>
-  </si>
-  <si>
-    <t>伤害</t>
-  </si>
-  <si>
-    <t>减益数值</t>
-  </si>
-  <si>
-    <t>持续时间</t>
-  </si>
-  <si>
-    <t>飞行速度</t>
-  </si>
-  <si>
-    <t>溅射半径</t>
   </si>
   <si>
     <t>普通箭矢</t>
@@ -291,7 +267,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -307,20 +283,26 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
@@ -840,189 +822,199 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1372,243 +1364,270 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9.29090909090909" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.71818181818182" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.4363636363636" style="1" customWidth="1"/>
-    <col min="4" max="4" width="33.8181818181818" style="2" customWidth="1"/>
-    <col min="5" max="5" width="60.4545454545455" style="2" customWidth="1"/>
-    <col min="6" max="6" width="107.454545454545" style="1" customWidth="1"/>
-    <col min="7" max="7" width="48.3636363636364" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.8636363636364" style="1" customWidth="1"/>
-    <col min="9" max="9" width="28.0090909090909" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.0090909090909" style="3" customWidth="1"/>
-    <col min="11" max="11" width="5.14545454545455" style="3" customWidth="1"/>
-    <col min="12" max="33" width="12.4363636363636" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.29090909090909" style="10" customWidth="1"/>
+    <col min="2" max="2" width="6.71818181818182" style="12" customWidth="1"/>
+    <col min="3" max="3" width="12.4363636363636" style="10" customWidth="1"/>
+    <col min="4" max="4" width="33.8181818181818" style="12" customWidth="1"/>
+    <col min="5" max="5" width="99" style="12" customWidth="1"/>
+    <col min="6" max="6" width="83" style="12" customWidth="1"/>
+    <col min="7" max="7" width="56.3636363636364" style="10" customWidth="1"/>
+    <col min="8" max="8" width="48.3636363636364" style="10" customWidth="1"/>
+    <col min="9" max="9" width="17.8636363636364" style="10" customWidth="1"/>
+    <col min="10" max="10" width="28.0090909090909" style="10" customWidth="1"/>
+    <col min="11" max="11" width="13.0090909090909" style="13" customWidth="1"/>
+    <col min="12" max="12" width="5.14545454545455" style="13" customWidth="1"/>
+    <col min="13" max="34" width="12.4363636363636" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.75" customHeight="1" spans="1:12">
-      <c r="A1" s="4" t="s">
+    <row r="1" ht="21.75" customHeight="1" spans="1:13">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="8"/>
-    </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:12">
-      <c r="A2" s="9" t="s">
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="16"/>
+    </row>
+    <row r="2" ht="21.75" customHeight="1" spans="1:13">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="8"/>
-    </row>
-    <row r="3" ht="21.75" customHeight="1" spans="1:12">
-      <c r="A3" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="10" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="16"/>
+    </row>
+    <row r="3" ht="21.75" customHeight="1" spans="1:13">
+      <c r="A3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="14" t="s">
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="D3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="8"/>
-    </row>
-    <row r="4" ht="22.5" customHeight="1" spans="1:12">
-      <c r="A4" s="4" t="s">
+      <c r="F3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5" t="s">
+      <c r="G3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="15"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="8"/>
-    </row>
-    <row r="5" ht="20.25" customHeight="1" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="H3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="I3" s="17"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="16"/>
+    </row>
+    <row r="4" ht="22.5" customHeight="1" spans="1:13">
+      <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="E4" s="4"/>
+      <c r="F4"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="20"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="16"/>
+    </row>
+    <row r="5" ht="20.25" customHeight="1" spans="1:13">
+      <c r="A5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="B5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="C5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="D5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-    </row>
-    <row r="6" ht="20.25" customHeight="1" spans="1:12">
-      <c r="B6" s="16">
+      <c r="E5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+    </row>
+    <row r="6" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B6" s="11">
         <v>10001</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="16">
+      <c r="C6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="11">
         <v>1</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-    </row>
-    <row r="7" ht="20.25" customHeight="1" spans="1:12">
-      <c r="B7" s="16">
+      <c r="F6">
+        <v>1.2</v>
+      </c>
+      <c r="H6" s="10">
+        <v>1</v>
+      </c>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+    </row>
+    <row r="7" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B7" s="11">
         <v>10002</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="16">
+      <c r="C7" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="11">
         <v>2</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-    </row>
-    <row r="8" ht="20.25" customHeight="1" spans="1:12">
-      <c r="B8" s="16">
+      <c r="F7">
+        <v>1.5</v>
+      </c>
+      <c r="H7" s="10">
+        <v>2</v>
+      </c>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+    </row>
+    <row r="8" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B8" s="11">
         <v>10003</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="16">
+      <c r="C8" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="11">
         <v>3</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-    </row>
-    <row r="9" ht="20.25" customHeight="1" spans="1:12">
-      <c r="B9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-    </row>
-    <row r="10" ht="20.25" customHeight="1" spans="1:12">
-      <c r="B10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-    </row>
-    <row r="11" ht="20.25" customHeight="1" spans="1:12">
-      <c r="B11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-    </row>
-    <row r="12" ht="20.25" customHeight="1" spans="1:12">
-      <c r="B12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-    </row>
-    <row r="13" ht="20.25" customHeight="1" spans="1:12">
-      <c r="B13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
-    </row>
-    <row r="14" ht="20.25" customHeight="1" spans="1:12">
-      <c r="B14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10">
+        <v>3</v>
+      </c>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+    </row>
+    <row r="9" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+    </row>
+    <row r="10" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="22"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+    </row>
+    <row r="11" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="22"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
+    </row>
+    <row r="12" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="22"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+    </row>
+    <row r="13" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="22"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+    </row>
+    <row r="14" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="22"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -1618,19 +1637,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="53.4545454545455" customWidth="1"/>
     <col min="3" max="3" width="38.1818181818182" customWidth="1"/>
-    <col min="4" max="4" width="25.1818181818182" customWidth="1"/>
-    <col min="5" max="5" width="25.4545454545455" customWidth="1"/>
-    <col min="6" max="6" width="24.6363636363636" customWidth="1"/>
-    <col min="7" max="7" width="23.5454545454545" customWidth="1"/>
-    <col min="8" max="8" width="29.1818181818182" customWidth="1"/>
+    <col min="4" max="5" width="25.1818181818182" customWidth="1"/>
+    <col min="6" max="6" width="25.4545454545455" customWidth="1"/>
+    <col min="7" max="7" width="24.6363636363636" customWidth="1"/>
+    <col min="8" max="8" width="23.5454545454545" customWidth="1"/>
+    <col min="9" max="9" width="29.1818181818182" customWidth="1"/>
+    <col min="10" max="10" width="19.4545454545455" customWidth="1"/>
+    <col min="11" max="11" width="25.8181818181818" customWidth="1"/>
+    <col min="12" max="12" width="34.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1641,10 +1663,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" t="s">
         <v>31</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>32</v>
@@ -1653,186 +1675,204 @@
         <v>33</v>
       </c>
       <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
         <v>34</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>35</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="E2" s="6"/>
+      <c r="L2" s="7"/>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
         <v>37</v>
       </c>
-      <c r="E3" t="s">
-        <v>8</v>
+      <c r="E3" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="L4" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
         <v>38</v>
       </c>
-      <c r="H3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="C5" t="s">
         <v>39</v>
       </c>
-      <c r="G4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>40</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
         <v>41</v>
       </c>
-      <c r="D5" t="s">
+      <c r="G5" t="s">
         <v>42</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
         <v>43</v>
       </c>
-      <c r="F5" t="s">
+      <c r="J5" t="s">
         <v>44</v>
       </c>
-      <c r="G5" t="s">
+      <c r="K5" t="s">
         <v>45</v>
       </c>
-      <c r="H5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" ht="14.5" spans="1:12">
       <c r="B6">
         <v>30001</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6">
+        <v>47</v>
+      </c>
+      <c r="E6" s="11">
+        <v>1</v>
+      </c>
+      <c r="F6">
         <v>100</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>8</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>1.2</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>1</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>2</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="14.5" spans="1:12">
       <c r="B7">
         <v>30002</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7">
+        <v>47</v>
+      </c>
+      <c r="E7" s="11">
+        <v>2</v>
+      </c>
+      <c r="F7">
         <v>250</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>15</v>
-      </c>
-      <c r="G7">
-        <v>1.5</v>
       </c>
       <c r="H7">
         <v>1.5</v>
       </c>
       <c r="I7">
+        <v>1.5</v>
+      </c>
+      <c r="J7">
         <v>5</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" ht="14.5" spans="1:12">
       <c r="B8">
         <v>40001</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8">
         <v>50</v>
       </c>
+      <c r="E8" s="11">
+        <v>3</v>
+      </c>
       <c r="F8">
+        <v>50</v>
+      </c>
+      <c r="G8">
         <v>5</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1841,36 +1881,48 @@
         <v>0</v>
       </c>
       <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" ht="14.5" spans="1:12">
       <c r="B9">
         <v>40002</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9">
+        <v>50</v>
+      </c>
+      <c r="E9" s="11">
+        <v>4</v>
+      </c>
+      <c r="F9">
         <v>120</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>12</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
         <v>3</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>2</v>
+      </c>
+      <c r="L9" s="10">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1882,16 +1934,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="49.3636363636364" customWidth="1"/>
     <col min="3" max="3" width="31.6363636363636" customWidth="1"/>
-    <col min="4" max="4" width="28.1818181818182" customWidth="1"/>
-    <col min="5" max="5" width="36.1818181818182" customWidth="1"/>
+    <col min="4" max="4" width="38.5454545454545" customWidth="1"/>
+    <col min="5" max="5" width="29.7272727272727" customWidth="1"/>
+    <col min="6" max="6" width="44" customWidth="1"/>
+    <col min="7" max="7" width="49.0909090909091" customWidth="1"/>
+    <col min="8" max="8" width="33.2727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1902,246 +1957,202 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" t="s">
         <v>55</v>
       </c>
-      <c r="E1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" t="s">
         <v>62</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F5" t="s">
         <v>63</v>
       </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="G5" t="s">
         <v>64</v>
       </c>
-      <c r="I4" t="s">
-        <v>64</v>
-      </c>
-      <c r="J4" t="s">
-        <v>64</v>
-      </c>
-      <c r="K4" t="s">
-        <v>64</v>
-      </c>
-      <c r="L4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="H5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" t="s">
-        <v>71</v>
-      </c>
-      <c r="I5" t="s">
-        <v>72</v>
-      </c>
-      <c r="J5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+    </row>
+    <row r="6" spans="1:8">
       <c r="B6">
         <v>20001</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="I6">
         <v>5</v>
       </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="B7">
         <v>20002</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F7">
-        <v>18</v>
-      </c>
-      <c r="I7">
         <v>6</v>
       </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="H7" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="B8">
         <v>20003</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8">
-        <v>30001</v>
-      </c>
-      <c r="I8">
+        <v>70</v>
+      </c>
+      <c r="F8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="H8" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="B9">
         <v>20004</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9">
-        <v>30002</v>
-      </c>
-      <c r="I9">
+        <v>70</v>
+      </c>
+      <c r="F9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="H9" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="B10">
         <v>20005</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>73</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
-      <c r="G10">
-        <v>0.15</v>
-      </c>
-      <c r="H10">
-        <v>2</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="H10" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="B11">
         <v>20006</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>73</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="G11">
-        <v>0.25</v>
-      </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
+      <c r="H11" s="3">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/局内.xlsx
+++ b/Configs/GameConfig/Datas/局内.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="基础建筑表" sheetId="1" r:id="rId1"/>
@@ -952,7 +952,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -964,13 +964,7 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1367,29 +1361,29 @@
   <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9.29090909090909" style="10" customWidth="1"/>
-    <col min="2" max="2" width="6.71818181818182" style="12" customWidth="1"/>
-    <col min="3" max="3" width="12.4363636363636" style="10" customWidth="1"/>
-    <col min="4" max="4" width="33.8181818181818" style="12" customWidth="1"/>
-    <col min="5" max="5" width="99" style="12" customWidth="1"/>
-    <col min="6" max="6" width="83" style="12" customWidth="1"/>
-    <col min="7" max="7" width="56.3636363636364" style="10" customWidth="1"/>
-    <col min="8" max="8" width="48.3636363636364" style="10" customWidth="1"/>
-    <col min="9" max="9" width="17.8636363636364" style="10" customWidth="1"/>
-    <col min="10" max="10" width="28.0090909090909" style="10" customWidth="1"/>
-    <col min="11" max="11" width="13.0090909090909" style="13" customWidth="1"/>
-    <col min="12" max="12" width="5.14545454545455" style="13" customWidth="1"/>
-    <col min="13" max="34" width="12.4363636363636" style="10" customWidth="1"/>
+    <col min="1" max="1" width="9.29090909090909" style="8" customWidth="1"/>
+    <col min="2" max="2" width="6.71818181818182" style="10" customWidth="1"/>
+    <col min="3" max="3" width="12.4363636363636" style="8" customWidth="1"/>
+    <col min="4" max="4" width="33.8181818181818" style="10" customWidth="1"/>
+    <col min="5" max="5" width="99" style="10" customWidth="1"/>
+    <col min="6" max="6" width="83" style="10" customWidth="1"/>
+    <col min="7" max="7" width="56.3636363636364" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.3636363636364" style="8" customWidth="1"/>
+    <col min="9" max="9" width="17.8636363636364" style="8" customWidth="1"/>
+    <col min="10" max="10" width="28.0090909090909" style="8" customWidth="1"/>
+    <col min="11" max="11" width="13.0090909090909" style="11" customWidth="1"/>
+    <col min="12" max="12" width="5.14545454545455" style="11" customWidth="1"/>
+    <col min="13" max="34" width="12.4363636363636" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1" spans="1:13">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
@@ -1401,228 +1395,228 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="16"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="14"/>
     </row>
     <row r="2" ht="21.75" customHeight="1" spans="1:13">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
       <c r="F2"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="16"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="14"/>
     </row>
     <row r="3" ht="21.75" customHeight="1" spans="1:13">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="16"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="14"/>
     </row>
     <row r="4" ht="22.5" customHeight="1" spans="1:13">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
+      <c r="C4" s="1"/>
       <c r="D4" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="1"/>
+      <c r="H4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="20"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="16"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" ht="20.25" customHeight="1" spans="1:13">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F5" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
     </row>
     <row r="6" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B6" s="11">
-        <v>10001</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="9">
+        <v>1</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="9">
         <v>1</v>
       </c>
       <c r="F6">
         <v>1.2</v>
       </c>
-      <c r="H6" s="10">
-        <v>1</v>
-      </c>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
+      <c r="H6" s="8">
+        <v>2</v>
+      </c>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
     </row>
     <row r="7" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B7" s="11">
-        <v>10002</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="9">
+        <v>2</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="9">
         <v>2</v>
       </c>
       <c r="F7">
         <v>1.5</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="8">
         <v>2</v>
       </c>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
     </row>
     <row r="8" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B8" s="11">
-        <v>10003</v>
-      </c>
-      <c r="C8" s="10" t="s">
+      <c r="B8" s="9">
+        <v>3</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <v>3</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
-      <c r="H8" s="10">
-        <v>3</v>
-      </c>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
+      <c r="H8" s="8">
+        <v>2</v>
+      </c>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
     </row>
     <row r="9" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
+      <c r="B9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
       <c r="F9"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
     </row>
     <row r="10" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="22"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
+      <c r="B10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="20"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
     </row>
     <row r="11" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="22"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
+      <c r="B11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="20"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
     </row>
     <row r="12" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="22"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
+      <c r="B12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="20"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
     </row>
     <row r="13" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="22"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
+      <c r="B13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="20"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
     </row>
     <row r="14" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="22"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
+      <c r="B14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="20"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1686,7 +1680,7 @@
       <c r="K1" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1694,8 +1688,8 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="L2" s="7"/>
+      <c r="E2" s="5"/>
+      <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
@@ -1710,7 +1704,7 @@
       <c r="D3" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
@@ -1731,7 +1725,7 @@
       <c r="K3" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1743,7 +1737,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="4"/>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1760,7 +1754,7 @@
       <c r="D5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F5" t="s">
@@ -1781,13 +1775,13 @@
       <c r="K5" t="s">
         <v>45</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="L5" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" ht="14.5" spans="1:12">
       <c r="B6">
-        <v>30001</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -1795,7 +1789,7 @@
       <c r="D6" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="9">
         <v>1</v>
       </c>
       <c r="F6">
@@ -1816,13 +1810,13 @@
       <c r="K6">
         <v>3</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="7" ht="14.5" spans="1:12">
       <c r="B7">
-        <v>30002</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
         <v>48</v>
@@ -1830,7 +1824,7 @@
       <c r="D7" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="9">
         <v>2</v>
       </c>
       <c r="F7">
@@ -1851,13 +1845,13 @@
       <c r="K7">
         <v>2.5</v>
       </c>
-      <c r="L7" s="10">
-        <v>2</v>
+      <c r="L7" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="14.5" spans="1:12">
       <c r="B8">
-        <v>40001</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
         <v>49</v>
@@ -1865,7 +1859,7 @@
       <c r="D8" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <v>3</v>
       </c>
       <c r="F8">
@@ -1886,13 +1880,13 @@
       <c r="K8">
         <v>1.5</v>
       </c>
-      <c r="L8" s="10">
-        <v>3</v>
+      <c r="L8" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="14.5" spans="1:12">
       <c r="B9">
-        <v>40002</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
         <v>51</v>
@@ -1900,7 +1894,7 @@
       <c r="D9" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="9">
         <v>4</v>
       </c>
       <c r="F9">
@@ -1921,8 +1915,8 @@
       <c r="K9">
         <v>2</v>
       </c>
-      <c r="L9" s="10">
-        <v>4</v>
+      <c r="L9" s="8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2043,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="B6">
-        <v>20001</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>66</v>
@@ -2061,12 +2055,12 @@
         <v>5</v>
       </c>
       <c r="H6" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="B7">
-        <v>20002</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
         <v>68</v>
@@ -2078,12 +2072,12 @@
         <v>6</v>
       </c>
       <c r="H7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="B8">
-        <v>20003</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
         <v>69</v>
@@ -2100,7 +2094,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="B9">
-        <v>20004</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
         <v>71</v>
@@ -2112,12 +2106,12 @@
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="B10">
-        <v>20005</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
         <v>72</v>
@@ -2132,12 +2126,12 @@
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="B11">
-        <v>20006</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
         <v>74</v>
@@ -2152,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/局内.xlsx
+++ b/Configs/GameConfig/Datas/局内.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="基础建筑表" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="86">
   <si>
     <t>##var</t>
   </si>
@@ -197,18 +197,27 @@
     <t>speed</t>
   </si>
   <si>
+    <t>damages</t>
+  </si>
+  <si>
     <t>buffs</t>
   </si>
   <si>
+    <t>pre_cast_anim_time</t>
+  </si>
+  <si>
+    <t>post_cast_anim_time</t>
+  </si>
+  <si>
     <t>EBulletType</t>
   </si>
   <si>
+    <t>CDamageEffect#sep=,</t>
+  </si>
+  <si>
     <t>int#ref=battle.TbBuff</t>
   </si>
   <si>
-    <t>s</t>
-  </si>
-  <si>
     <t>子弹id</t>
   </si>
   <si>
@@ -227,6 +236,12 @@
     <t>施加buff</t>
   </si>
   <si>
+    <t>前摇动画间隔</t>
+  </si>
+  <si>
+    <t>后摇动画间隔</t>
+  </si>
+  <si>
     <t>预制体路径</t>
   </si>
   <si>
@@ -236,25 +251,43 @@
     <t>PROJECTILE</t>
   </si>
   <si>
+    <t>Physical,10</t>
+  </si>
+  <si>
     <t>强化箭矢</t>
   </si>
   <si>
+    <t>Physical,11</t>
+  </si>
+  <si>
     <t>召唤士兵</t>
   </si>
   <si>
     <t>SPAWN_UNIT</t>
   </si>
   <si>
+    <t>Physical,12</t>
+  </si>
+  <si>
     <t>召唤骑士</t>
   </si>
   <si>
+    <t>Physical,13</t>
+  </si>
+  <si>
     <t>攻击光环</t>
   </si>
   <si>
     <t>INSTANT_AURA</t>
   </si>
   <si>
+    <t>Physical,14</t>
+  </si>
+  <si>
     <t>狂热光环</t>
+  </si>
+  <si>
+    <t>Physical,15</t>
   </si>
 </sst>
 </file>
@@ -1928,19 +1961,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="49.3636363636364" customWidth="1"/>
     <col min="3" max="3" width="31.6363636363636" customWidth="1"/>
     <col min="4" max="4" width="38.5454545454545" customWidth="1"/>
-    <col min="5" max="5" width="29.7272727272727" customWidth="1"/>
-    <col min="6" max="6" width="44" customWidth="1"/>
-    <col min="7" max="7" width="49.0909090909091" customWidth="1"/>
-    <col min="8" max="8" width="33.2727272727273" customWidth="1"/>
+    <col min="5" max="5" width="15.5" customWidth="1"/>
+    <col min="6" max="6" width="22.7818181818182" customWidth="1"/>
+    <col min="7" max="7" width="19.7818181818182" customWidth="1"/>
+    <col min="8" max="8" width="17.9636363636364" customWidth="1"/>
+    <col min="9" max="9" width="29.7272727272727" customWidth="1"/>
+    <col min="10" max="10" width="17.9636363636364" customWidth="1"/>
+    <col min="11" max="11" width="33.2727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1962,17 +1998,26 @@
       <c r="G1" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" t="s">
+        <v>58</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1983,7 +2028,7 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1992,132 +2037,186 @@
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+      <c r="K4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G5" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>66</v>
+      </c>
+      <c r="H5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J5" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="H6" s="3">
+        <v>45</v>
+      </c>
+      <c r="G6" t="s">
+        <v>73</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0.1</v>
+      </c>
+      <c r="J6">
+        <v>0.2</v>
+      </c>
+      <c r="K6" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:11">
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F7">
         <v>6</v>
       </c>
-      <c r="H7" s="3">
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0.2</v>
+      </c>
+      <c r="J7">
+        <v>0.2</v>
+      </c>
+      <c r="K7" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:11">
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
-      <c r="H8" s="3">
+      <c r="G8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0.2</v>
+      </c>
+      <c r="J8">
+        <v>0.2</v>
+      </c>
+      <c r="K8" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:11">
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
-      <c r="H9" s="3">
+      <c r="G9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0.2</v>
+      </c>
+      <c r="J9">
+        <v>0.2</v>
+      </c>
+      <c r="K9" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:11">
       <c r="B10">
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -2125,19 +2224,31 @@
       <c r="F10">
         <v>0</v>
       </c>
-      <c r="H10" s="3">
+      <c r="G10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0.2</v>
+      </c>
+      <c r="J10">
+        <v>0.2</v>
+      </c>
+      <c r="K10" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:11">
       <c r="B11">
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -2145,7 +2256,19 @@
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="H11" s="3">
+      <c r="G11" t="s">
+        <v>85</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0.2</v>
+      </c>
+      <c r="J11">
+        <v>0.2</v>
+      </c>
+      <c r="K11" s="3">
         <v>3</v>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/局内.xlsx
+++ b/Configs/GameConfig/Datas/局内.xlsx
@@ -12,7 +12,7 @@
     <sheet name="子弹表" sheetId="2" r:id="rId3"/>
     <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>##var</t>
   </si>
@@ -840,207 +840,207 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="0" applyFont="0" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="0" applyFill="0" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="0" applyFill="0" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="5" applyFill="1" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="6" applyFill="1" borderId="9" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="10" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="0" applyFill="0" borderId="11" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="0" applyFill="0" borderId="12" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" applyNumberFormat="1" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" applyNumberFormat="1" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="3" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="4" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1387,29 +1387,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9.29090909090909" style="8" customWidth="1"/>
-    <col min="2" max="2" width="6.71818181818182" style="10" customWidth="1"/>
-    <col min="3" max="3" width="12.4363636363636" style="8" customWidth="1"/>
-    <col min="4" max="4" width="33.8181818181818" style="10" customWidth="1"/>
-    <col min="5" max="5" width="99" style="10" customWidth="1"/>
-    <col min="6" max="6" width="83" style="10" customWidth="1"/>
-    <col min="7" max="7" width="56.3636363636364" style="8" customWidth="1"/>
-    <col min="8" max="8" width="48.3636363636364" style="8" customWidth="1"/>
-    <col min="9" max="9" width="17.8636363636364" style="8" customWidth="1"/>
-    <col min="10" max="10" width="28.0090909090909" style="8" customWidth="1"/>
-    <col min="11" max="11" width="13.0090909090909" style="11" customWidth="1"/>
-    <col min="12" max="12" width="5.14545454545455" style="11" customWidth="1"/>
-    <col min="13" max="34" width="12.4363636363636" style="8" customWidth="1"/>
+    <col min="1" max="1" width="9.29090909090909" customWidth="1" style="8"/>
+    <col min="2" max="2" width="6.71818181818182" customWidth="1" style="10"/>
+    <col min="3" max="3" width="12.4363636363636" customWidth="1" style="8"/>
+    <col min="4" max="4" width="33.8181818181818" customWidth="1" style="10"/>
+    <col min="5" max="5" width="99" customWidth="1" style="10"/>
+    <col min="6" max="6" width="83" customWidth="1" style="10"/>
+    <col min="7" max="7" width="56.3636363636364" customWidth="1" style="8"/>
+    <col min="8" max="8" width="48.3636363636364" customWidth="1" style="8"/>
+    <col min="9" max="9" width="17.8636363636364" customWidth="1" style="8"/>
+    <col min="10" max="10" width="28.0090909090909" customWidth="1" style="8"/>
+    <col min="11" max="11" width="13.0090909090909" customWidth="1" style="11"/>
+    <col min="12" max="12" width="5.14545454545455" customWidth="1" style="11"/>
+    <col min="13" max="34" width="12.4363636363636" customWidth="1" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.75" customHeight="1" spans="1:13">
+    <row r="1" ht="21.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1425,7 +1425,7 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1440,7 +1440,7 @@
       <c r="L1" s="13"/>
       <c r="M1" s="14"/>
     </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:13">
+    <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1457,7 +1457,7 @@
       <c r="L2" s="17"/>
       <c r="M2" s="14"/>
     </row>
-    <row r="3" ht="21.75" customHeight="1" spans="1:13">
+    <row r="3" ht="21.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -1473,7 +1473,7 @@
       <c r="E3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="0" t="s">
         <v>12</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -1488,7 +1488,7 @@
       <c r="L3" s="17"/>
       <c r="M3" s="14"/>
     </row>
-    <row r="4" ht="22.5" customHeight="1" spans="1:13">
+    <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1509,7 +1509,7 @@
       <c r="L4" s="1"/>
       <c r="M4" s="14"/>
     </row>
-    <row r="5" ht="20.25" customHeight="1" spans="1:13">
+    <row r="5" ht="20.25" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>17</v>
       </c>
@@ -1525,7 +1525,7 @@
       <c r="E5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="0" t="s">
         <v>22</v>
       </c>
       <c r="G5" s="8" t="s">
@@ -1537,7 +1537,7 @@
       <c r="K5" s="19"/>
       <c r="L5" s="19"/>
     </row>
-    <row r="6" ht="20.25" customHeight="1" spans="1:13">
+    <row r="6" ht="20.25" customHeight="1">
       <c r="B6" s="9">
         <v>1</v>
       </c>
@@ -1550,7 +1550,7 @@
       <c r="E6" s="9">
         <v>1</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="0">
         <v>1.2</v>
       </c>
       <c r="H6" s="8">
@@ -1559,7 +1559,7 @@
       <c r="K6" s="19"/>
       <c r="L6" s="19"/>
     </row>
-    <row r="7" ht="20.25" customHeight="1" spans="1:13">
+    <row r="7" ht="20.25" customHeight="1">
       <c r="B7" s="9">
         <v>2</v>
       </c>
@@ -1572,7 +1572,7 @@
       <c r="E7" s="9">
         <v>2</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="0">
         <v>1.5</v>
       </c>
       <c r="H7" s="8">
@@ -1581,7 +1581,7 @@
       <c r="K7" s="19"/>
       <c r="L7" s="19"/>
     </row>
-    <row r="8" ht="20.25" customHeight="1" spans="1:13">
+    <row r="8" ht="20.25" customHeight="1">
       <c r="B8" s="9">
         <v>3</v>
       </c>
@@ -1594,7 +1594,7 @@
       <c r="E8" s="9">
         <v>3</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="0">
         <v>0</v>
       </c>
       <c r="H8" s="8">
@@ -1603,7 +1603,7 @@
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
     </row>
-    <row r="9" ht="20.25" customHeight="1" spans="1:13">
+    <row r="9" ht="20.25" customHeight="1">
       <c r="B9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -1611,7 +1611,7 @@
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
     </row>
-    <row r="10" ht="20.25" customHeight="1" spans="1:13">
+    <row r="10" ht="20.25" customHeight="1">
       <c r="B10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -1619,7 +1619,7 @@
       <c r="K10" s="19"/>
       <c r="L10" s="19"/>
     </row>
-    <row r="11" ht="20.25" customHeight="1" spans="1:13">
+    <row r="11" ht="20.25" customHeight="1">
       <c r="B11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -1627,7 +1627,7 @@
       <c r="K11" s="19"/>
       <c r="L11" s="19"/>
     </row>
-    <row r="12" ht="20.25" customHeight="1" spans="1:13">
+    <row r="12" ht="20.25" customHeight="1">
       <c r="B12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -1635,7 +1635,7 @@
       <c r="K12" s="19"/>
       <c r="L12" s="19"/>
     </row>
-    <row r="13" ht="20.25" customHeight="1" spans="1:13">
+    <row r="13" ht="20.25" customHeight="1">
       <c r="B13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
@@ -1643,7 +1643,7 @@
       <c r="K13" s="19"/>
       <c r="L13" s="19"/>
     </row>
-    <row r="14" ht="20.25" customHeight="1" spans="1:13">
+    <row r="14" ht="20.25" customHeight="1">
       <c r="B14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
@@ -1652,7 +1652,7 @@
       <c r="L14" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
@@ -1662,7 +1662,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
   <sheetPr/>
   <dimension ref="A1:L9"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
@@ -1679,94 +1679,94 @@
     <col min="12" max="12" width="34.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>31</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="0" t="s">
         <v>36</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="0" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="5"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="0" t="s">
         <v>37</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="0" t="s">
         <v>12</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
+    <row r="4">
+      <c r="A4" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="0" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="4"/>
@@ -1774,178 +1774,178 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
+    <row r="5">
+      <c r="A5" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="0" t="s">
         <v>40</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" ht="14.5" spans="1:12">
-      <c r="B6">
+    <row r="6" ht="14.5">
+      <c r="B6" s="0">
         <v>1</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="0" t="s">
         <v>47</v>
       </c>
       <c r="E6" s="9">
         <v>1</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="0">
         <v>100</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="0">
         <v>8</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="0">
         <v>1.2</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="0">
         <v>1</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="0">
         <v>2</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="0">
         <v>3</v>
       </c>
       <c r="L6" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="7" ht="14.5" spans="1:12">
-      <c r="B7">
+    <row r="7" ht="14.5">
+      <c r="B7" s="0">
         <v>2</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="0" t="s">
         <v>47</v>
       </c>
       <c r="E7" s="9">
         <v>2</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="0">
         <v>250</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="0">
         <v>15</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="0">
         <v>1.5</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="0">
         <v>1.5</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="0">
         <v>5</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="0">
         <v>2.5</v>
       </c>
       <c r="L7" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="8" ht="14.5" spans="1:12">
-      <c r="B8">
+    <row r="8" ht="14.5">
+      <c r="B8" s="0">
         <v>3</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E8" s="9">
         <v>3</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="0">
         <v>50</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="0">
         <v>5</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="0">
         <v>0</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="0">
         <v>0</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="0">
         <v>0</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="0">
         <v>1.5</v>
       </c>
       <c r="L8" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" ht="14.5" spans="1:12">
-      <c r="B9">
+    <row r="9" ht="14.5">
+      <c r="B9" s="0">
         <v>4</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E9" s="9">
         <v>4</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="0">
         <v>120</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="0">
         <v>12</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="0">
         <v>0</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="0">
         <v>0</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="0">
         <v>3</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="0">
         <v>2</v>
       </c>
       <c r="L9" s="8">
@@ -1959,7 +1959,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
   <sheetPr/>
   <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
@@ -1976,296 +1976,296 @@
     <col min="11" max="11" width="33.2727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="0" t="s">
         <v>58</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="0" t="s">
         <v>0</v>
       </c>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="0" t="s">
         <v>12</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
+    <row r="4">
+      <c r="A4" s="0" t="s">
         <v>15</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
+    <row r="5">
+      <c r="A5" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="0" t="s">
         <v>69</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="B6">
+    <row r="6">
+      <c r="B6" s="0">
         <v>1</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="0">
         <v>45</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="0">
         <v>0</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="0">
         <v>0.1</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="0">
         <v>0.2</v>
       </c>
       <c r="K6" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
-      <c r="B7">
+    <row r="7">
+      <c r="B7" s="0">
         <v>2</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="0">
         <v>6</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="0">
         <v>0</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="0">
         <v>0.2</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="0">
         <v>0.2</v>
       </c>
       <c r="K7" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
-      <c r="B8">
+    <row r="8">
+      <c r="B8" s="0">
         <v>3</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="0">
         <v>0</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="0">
         <v>0</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="0">
         <v>0.2</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="0">
         <v>0.2</v>
       </c>
       <c r="K8" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
-      <c r="B9">
+    <row r="9">
+      <c r="B9" s="0">
         <v>4</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="0">
         <v>0</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="0" t="s">
         <v>80</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="0">
         <v>0</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="0">
         <v>0.2</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="0">
         <v>0.2</v>
       </c>
       <c r="K9" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
-      <c r="B10">
+    <row r="10">
+      <c r="B10" s="0">
         <v>5</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="0">
         <v>2</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="0">
         <v>0</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="0">
         <v>0</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="0">
         <v>0.2</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="0">
         <v>0.2</v>
       </c>
       <c r="K10" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
-      <c r="B11">
+    <row r="11">
+      <c r="B11" s="0">
         <v>6</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="0" t="s">
         <v>84</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="0">
         <v>2</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="0">
         <v>0</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="0">
         <v>0</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="0">
         <v>0.2</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="0">
         <v>0.2</v>
       </c>
       <c r="K11" s="3">
@@ -2279,12 +2279,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
   <sheetPr/>
-  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to AION.CoreGame under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>
--- a/Configs/GameConfig/Datas/局内.xlsx
+++ b/Configs/GameConfig/Datas/局内.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="基础建筑表" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="子弹表" sheetId="2" r:id="rId3"/>
     <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="98">
   <si>
     <t>##var</t>
   </si>
@@ -107,22 +107,34 @@
     <t>模型</t>
   </si>
   <si>
-    <t>箭塔</t>
-  </si>
-  <si>
-    <t>基础单体攻击塔</t>
-  </si>
-  <si>
-    <t>兵营</t>
-  </si>
-  <si>
-    <t>持续生成士兵</t>
-  </si>
-  <si>
-    <t>鼓舞战旗</t>
-  </si>
-  <si>
-    <t>增加周围友军攻击力</t>
+    <t>法师营地</t>
+  </si>
+  <si>
+    <t>训练法师单位的建筑</t>
+  </si>
+  <si>
+    <t>战士营地</t>
+  </si>
+  <si>
+    <t>训练战士单位的建筑</t>
+  </si>
+  <si>
+    <t>骑士营地</t>
+  </si>
+  <si>
+    <t>训练骑士单位的建筑</t>
+  </si>
+  <si>
+    <t>射手营地</t>
+  </si>
+  <si>
+    <t>训练弓箭手单位的建筑</t>
+  </si>
+  <si>
+    <t>弓箭塔</t>
+  </si>
+  <si>
+    <t>远程攻击防御建筑</t>
   </si>
   <si>
     <t>unit_type</t>
@@ -170,22 +182,28 @@
     <t>移动速度</t>
   </si>
   <si>
-    <t>民兵</t>
+    <t>战士</t>
   </si>
   <si>
     <t>HERO</t>
   </si>
   <si>
+    <t>法师</t>
+  </si>
+  <si>
+    <t>弓箭手</t>
+  </si>
+  <si>
     <t>骑士</t>
   </si>
   <si>
-    <t>史莱姆</t>
+    <t>不死族</t>
   </si>
   <si>
     <t>ENEMY</t>
   </si>
   <si>
-    <t>兽人战士</t>
+    <t>不死族首领</t>
   </si>
   <si>
     <t>bullet_type</t>
@@ -245,49 +263,67 @@
     <t>预制体路径</t>
   </si>
   <si>
-    <t>普通箭矢</t>
+    <t>战士普攻</t>
+  </si>
+  <si>
+    <t>MELEE</t>
+  </si>
+  <si>
+    <t>Physical,10</t>
+  </si>
+  <si>
+    <t>法师普攻</t>
   </si>
   <si>
     <t>PROJECTILE</t>
   </si>
   <si>
-    <t>Physical,10</t>
-  </si>
-  <si>
-    <t>强化箭矢</t>
-  </si>
-  <si>
-    <t>Physical,11</t>
-  </si>
-  <si>
-    <t>召唤士兵</t>
+    <t>Magical,20</t>
+  </si>
+  <si>
+    <t>弓箭手箭矢</t>
+  </si>
+  <si>
+    <t>Physical,15</t>
+  </si>
+  <si>
+    <t>骑士普攻</t>
+  </si>
+  <si>
+    <t>Physical,25</t>
+  </si>
+  <si>
+    <t>不死族普攻</t>
+  </si>
+  <si>
+    <t>Physical,8</t>
+  </si>
+  <si>
+    <t>不死族首领普攻</t>
+  </si>
+  <si>
+    <t>Physical,35</t>
+  </si>
+  <si>
+    <t>法师生成子弹</t>
   </si>
   <si>
     <t>SPAWN_UNIT</t>
   </si>
   <si>
-    <t>Physical,12</t>
-  </si>
-  <si>
-    <t>召唤骑士</t>
-  </si>
-  <si>
-    <t>Physical,13</t>
-  </si>
-  <si>
-    <t>攻击光环</t>
-  </si>
-  <si>
-    <t>INSTANT_AURA</t>
-  </si>
-  <si>
-    <t>Physical,14</t>
-  </si>
-  <si>
-    <t>狂热光环</t>
-  </si>
-  <si>
-    <t>Physical,15</t>
+    <t>Physical,0</t>
+  </si>
+  <si>
+    <t>战士生成子弹</t>
+  </si>
+  <si>
+    <t>骑士生成子弹</t>
+  </si>
+  <si>
+    <t>射手生成子弹</t>
+  </si>
+  <si>
+    <t>防御箭塔子弹</t>
   </si>
 </sst>
 </file>
@@ -840,207 +876,207 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="0" applyFont="0" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="0" applyFill="0" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="0" applyFill="0" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="5" applyFill="1" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="6" applyFill="1" borderId="9" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="10" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="0" applyFill="0" borderId="11" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="0" applyFill="0" borderId="12" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="24" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" applyNumberFormat="1" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" applyNumberFormat="1" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="3" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="4" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1387,29 +1423,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9.29090909090909" customWidth="1" style="8"/>
-    <col min="2" max="2" width="6.71818181818182" customWidth="1" style="10"/>
-    <col min="3" max="3" width="12.4363636363636" customWidth="1" style="8"/>
-    <col min="4" max="4" width="33.8181818181818" customWidth="1" style="10"/>
-    <col min="5" max="5" width="99" customWidth="1" style="10"/>
-    <col min="6" max="6" width="83" customWidth="1" style="10"/>
-    <col min="7" max="7" width="56.3636363636364" customWidth="1" style="8"/>
-    <col min="8" max="8" width="48.3636363636364" customWidth="1" style="8"/>
-    <col min="9" max="9" width="17.8636363636364" customWidth="1" style="8"/>
-    <col min="10" max="10" width="28.0090909090909" customWidth="1" style="8"/>
-    <col min="11" max="11" width="13.0090909090909" customWidth="1" style="11"/>
-    <col min="12" max="12" width="5.14545454545455" customWidth="1" style="11"/>
-    <col min="13" max="34" width="12.4363636363636" customWidth="1" style="8"/>
+    <col min="1" max="1" width="9.29090909090909" style="8" customWidth="1"/>
+    <col min="2" max="2" width="6.71818181818182" style="10" customWidth="1"/>
+    <col min="3" max="3" width="12.4363636363636" style="8" customWidth="1"/>
+    <col min="4" max="4" width="33.8181818181818" style="10" customWidth="1"/>
+    <col min="5" max="5" width="99" style="10" customWidth="1"/>
+    <col min="6" max="6" width="83" style="10" customWidth="1"/>
+    <col min="7" max="7" width="56.3636363636364" style="8" customWidth="1"/>
+    <col min="8" max="8" width="48.3636363636364" style="8" customWidth="1"/>
+    <col min="9" max="9" width="17.8636363636364" style="8" customWidth="1"/>
+    <col min="10" max="10" width="28.0090909090909" style="8" customWidth="1"/>
+    <col min="11" max="11" width="13.0090909090909" style="11" customWidth="1"/>
+    <col min="12" max="12" width="5.14545454545455" style="11" customWidth="1"/>
+    <col min="13" max="34" width="12.4363636363636" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.75" customHeight="1">
+    <row r="1" ht="21.75" customHeight="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1425,7 +1461,7 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1440,7 +1476,7 @@
       <c r="L1" s="13"/>
       <c r="M1" s="14"/>
     </row>
-    <row r="2" ht="21.75" customHeight="1">
+    <row r="2" ht="21.75" customHeight="1" spans="1:13">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1457,7 +1493,7 @@
       <c r="L2" s="17"/>
       <c r="M2" s="14"/>
     </row>
-    <row r="3" ht="21.75" customHeight="1">
+    <row r="3" ht="21.75" customHeight="1" spans="1:13">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -1473,7 +1509,7 @@
       <c r="E3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" t="s">
         <v>12</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -1488,7 +1524,7 @@
       <c r="L3" s="17"/>
       <c r="M3" s="14"/>
     </row>
-    <row r="4" ht="22.5" customHeight="1">
+    <row r="4" ht="22.5" customHeight="1" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1509,7 +1545,7 @@
       <c r="L4" s="1"/>
       <c r="M4" s="14"/>
     </row>
-    <row r="5" ht="20.25" customHeight="1">
+    <row r="5" ht="20.25" customHeight="1" spans="1:13">
       <c r="A5" s="8" t="s">
         <v>17</v>
       </c>
@@ -1525,7 +1561,7 @@
       <c r="E5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" t="s">
         <v>22</v>
       </c>
       <c r="G5" s="8" t="s">
@@ -1537,9 +1573,9 @@
       <c r="K5" s="19"/>
       <c r="L5" s="19"/>
     </row>
-    <row r="6" ht="20.25" customHeight="1">
+    <row r="6" ht="20.25" customHeight="1" spans="1:13">
       <c r="B6" s="9">
-        <v>1</v>
+        <v>3001</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>25</v>
@@ -1548,20 +1584,23 @@
         <v>26</v>
       </c>
       <c r="E6" s="9">
-        <v>1</v>
-      </c>
-      <c r="F6" s="0">
-        <v>1.2</v>
+        <v>13001</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0</v>
       </c>
       <c r="H6" s="8">
-        <v>2</v>
+        <v>3001</v>
       </c>
       <c r="K6" s="19"/>
       <c r="L6" s="19"/>
     </row>
-    <row r="7" ht="20.25" customHeight="1">
+    <row r="7" ht="20.25" customHeight="1" spans="1:13">
       <c r="B7" s="9">
-        <v>2</v>
+        <v>3002</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>27</v>
@@ -1570,20 +1609,23 @@
         <v>28</v>
       </c>
       <c r="E7" s="9">
-        <v>2</v>
-      </c>
-      <c r="F7" s="0">
-        <v>1.5</v>
+        <v>13002</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0</v>
       </c>
       <c r="H7" s="8">
-        <v>2</v>
+        <v>3002</v>
       </c>
       <c r="K7" s="19"/>
       <c r="L7" s="19"/>
     </row>
-    <row r="8" ht="20.25" customHeight="1">
+    <row r="8" ht="20.25" customHeight="1" spans="1:13">
       <c r="B8" s="9">
-        <v>3</v>
+        <v>3003</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>29</v>
@@ -1592,34 +1634,71 @@
         <v>30</v>
       </c>
       <c r="E8" s="9">
-        <v>3</v>
-      </c>
-      <c r="F8" s="0">
+        <v>13003</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="8">
         <v>0</v>
       </c>
       <c r="H8" s="8">
-        <v>2</v>
+        <v>3003</v>
       </c>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
     </row>
-    <row r="9" ht="20.25" customHeight="1">
-      <c r="B9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9"/>
+    <row r="9" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B9" s="9">
+        <v>3004</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="9">
+        <v>13004</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0</v>
+      </c>
+      <c r="H9" s="8">
+        <v>3004</v>
+      </c>
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
     </row>
-    <row r="10" ht="20.25" customHeight="1">
-      <c r="B10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="20"/>
+    <row r="10" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B10" s="9">
+        <v>3005</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="9">
+        <v>13005</v>
+      </c>
+      <c r="F10" s="20">
+        <v>6</v>
+      </c>
+      <c r="G10" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="H10" s="8">
+        <v>3005</v>
+      </c>
       <c r="K10" s="19"/>
       <c r="L10" s="19"/>
     </row>
-    <row r="11" ht="20.25" customHeight="1">
+    <row r="11" ht="20.25" customHeight="1" spans="1:13">
       <c r="B11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -1627,7 +1706,7 @@
       <c r="K11" s="19"/>
       <c r="L11" s="19"/>
     </row>
-    <row r="12" ht="20.25" customHeight="1">
+    <row r="12" ht="20.25" customHeight="1" spans="1:13">
       <c r="B12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -1635,7 +1714,7 @@
       <c r="K12" s="19"/>
       <c r="L12" s="19"/>
     </row>
-    <row r="13" ht="20.25" customHeight="1">
+    <row r="13" ht="20.25" customHeight="1" spans="1:13">
       <c r="B13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
@@ -1643,7 +1722,7 @@
       <c r="K13" s="19"/>
       <c r="L13" s="19"/>
     </row>
-    <row r="14" ht="20.25" customHeight="1">
+    <row r="14" ht="20.25" customHeight="1" spans="1:13">
       <c r="B14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
@@ -1652,7 +1731,7 @@
       <c r="L14" s="19"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="2">
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
@@ -1662,9 +1741,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="53.4545454545455" customWidth="1"/>
@@ -1677,279 +1756,365 @@
     <col min="10" max="10" width="19.4545454545455" customWidth="1"/>
     <col min="11" max="11" width="25.8181818181818" customWidth="1"/>
     <col min="12" max="12" width="34.1818181818182" customWidth="1"/>
+    <col min="13" max="13" width="29.2727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
-        <v>31</v>
-      </c>
       <c r="E1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="H1" s="0" t="s">
+      <c r="G1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>36</v>
+      <c r="J1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" t="s">
+        <v>39</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="5"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>37</v>
-      </c>
       <c r="E3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="H3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="I3" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="J3" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="0" t="s">
+      <c r="K3" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="0" t="s">
+      <c r="L3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="1"/>
+      <c r="M4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>40</v>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
       </c>
       <c r="E5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="0" t="s">
+      <c r="G5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="J5" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" s="0" t="s">
-        <v>45</v>
+      <c r="J5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" t="s">
+        <v>48</v>
       </c>
       <c r="L5" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" ht="14.5">
-      <c r="B6" s="0">
+    <row r="6" ht="14.5" spans="1:13">
+      <c r="C6">
+        <v>1001</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6">
+        <v>11001</v>
+      </c>
+      <c r="G6">
+        <v>200</v>
+      </c>
+      <c r="H6">
+        <v>15</v>
+      </c>
+      <c r="I6">
+        <v>1.5</v>
+      </c>
+      <c r="J6">
         <v>1</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6" s="8">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="7" ht="14.5" spans="1:13">
+      <c r="C7">
+        <v>1002</v>
+      </c>
+      <c r="D7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7">
+        <v>11002</v>
+      </c>
+      <c r="G7">
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>25</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7">
+        <v>1.5</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="M7">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="8" ht="14.5" spans="1:13">
+      <c r="C8">
+        <v>1003</v>
+      </c>
+      <c r="D8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8">
+        <v>11003</v>
+      </c>
+      <c r="G8">
+        <v>150</v>
+      </c>
+      <c r="H8">
+        <v>12</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <v>1.2</v>
+      </c>
+      <c r="K8">
+        <v>3</v>
+      </c>
+      <c r="L8" s="8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="9" ht="14.5" spans="1:13">
+      <c r="C9">
+        <v>1004</v>
+      </c>
+      <c r="D9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9">
+        <v>11004</v>
+      </c>
+      <c r="G9">
+        <v>300</v>
+      </c>
+      <c r="H9">
+        <v>20</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>1.5</v>
+      </c>
+      <c r="K9">
+        <v>8</v>
+      </c>
+      <c r="L9" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="M9">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="C10">
+        <v>2001</v>
+      </c>
+      <c r="D10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10">
+        <v>12001</v>
+      </c>
+      <c r="G10">
+        <v>80</v>
+      </c>
+      <c r="H10">
+        <v>10</v>
+      </c>
+      <c r="I10">
         <v>1</v>
       </c>
-      <c r="F6" s="0">
-        <v>100</v>
-      </c>
-      <c r="G6" s="0">
-        <v>8</v>
-      </c>
-      <c r="H6" s="0">
-        <v>1.2</v>
-      </c>
-      <c r="I6" s="0">
-        <v>1</v>
-      </c>
-      <c r="J6" s="0">
+      <c r="J10">
+        <v>0.8</v>
+      </c>
+      <c r="K10">
         <v>2</v>
       </c>
-      <c r="K6" s="0">
-        <v>3</v>
-      </c>
-      <c r="L6" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="14.5">
-      <c r="B7" s="0">
+      <c r="L10">
+        <v>2.5</v>
+      </c>
+      <c r="M10">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="C11">
+        <v>2002</v>
+      </c>
+      <c r="D11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11">
+        <v>12002</v>
+      </c>
+      <c r="G11">
+        <v>500</v>
+      </c>
+      <c r="H11">
+        <v>35</v>
+      </c>
+      <c r="I11">
+        <v>2.5</v>
+      </c>
+      <c r="J11">
         <v>2</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="9">
+      <c r="K11">
+        <v>12</v>
+      </c>
+      <c r="L11">
         <v>2</v>
       </c>
-      <c r="F7" s="0">
-        <v>250</v>
-      </c>
-      <c r="G7" s="0">
-        <v>15</v>
-      </c>
-      <c r="H7" s="0">
-        <v>1.5</v>
-      </c>
-      <c r="I7" s="0">
-        <v>1.5</v>
-      </c>
-      <c r="J7" s="0">
-        <v>5</v>
-      </c>
-      <c r="K7" s="0">
-        <v>2.5</v>
-      </c>
-      <c r="L7" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="14.5">
-      <c r="B8" s="0">
-        <v>3</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" s="9">
-        <v>3</v>
-      </c>
-      <c r="F8" s="0">
-        <v>50</v>
-      </c>
-      <c r="G8" s="0">
-        <v>5</v>
-      </c>
-      <c r="H8" s="0">
-        <v>0</v>
-      </c>
-      <c r="I8" s="0">
-        <v>0</v>
-      </c>
-      <c r="J8" s="0">
-        <v>0</v>
-      </c>
-      <c r="K8" s="0">
-        <v>1.5</v>
-      </c>
-      <c r="L8" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="14.5">
-      <c r="B9" s="0">
-        <v>4</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="9">
-        <v>4</v>
-      </c>
-      <c r="F9" s="0">
-        <v>120</v>
-      </c>
-      <c r="G9" s="0">
-        <v>12</v>
-      </c>
-      <c r="H9" s="0">
-        <v>0</v>
-      </c>
-      <c r="I9" s="0">
-        <v>0</v>
-      </c>
-      <c r="J9" s="0">
-        <v>3</v>
-      </c>
-      <c r="K9" s="0">
-        <v>2</v>
-      </c>
-      <c r="L9" s="8">
-        <v>1</v>
+      <c r="M11">
+        <v>2002</v>
       </c>
     </row>
   </sheetData>
@@ -1959,9 +2124,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="49.3636363636364" customWidth="1"/>
@@ -1974,302 +2139,491 @@
     <col min="9" max="9" width="29.7272727272727" customWidth="1"/>
     <col min="10" max="10" width="17.9636363636364" customWidth="1"/>
     <col min="11" max="11" width="33.2727272727273" customWidth="1"/>
+    <col min="12" max="12" width="49.6181818181818" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="J1" s="0" t="s">
+      <c r="E1" t="s">
         <v>58</v>
       </c>
+      <c r="F1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" t="s">
+        <v>63</v>
+      </c>
       <c r="K1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="K2" s="2"/>
     </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="G3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="I3" s="0" t="s">
+      <c r="H3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="0" t="s">
+      <c r="K3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="I5" s="0" t="s">
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
         <v>68</v>
       </c>
-      <c r="J5" s="0" t="s">
+      <c r="D5" t="s">
         <v>69</v>
       </c>
+      <c r="E5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H5"/>
+      <c r="I5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" t="s">
+        <v>74</v>
+      </c>
       <c r="K5" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="0">
-        <v>1</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="F6" s="0">
+        <v>75</v>
+      </c>
+      <c r="L5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="C6">
+        <v>11001</v>
+      </c>
+      <c r="D6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>45</v>
       </c>
-      <c r="G6" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="H6" s="0">
-        <v>0</v>
-      </c>
-      <c r="I6" s="0">
+      <c r="H6" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
         <v>0.1</v>
       </c>
-      <c r="J6" s="0">
+      <c r="K6" s="3">
         <v>0.2</v>
       </c>
-      <c r="K6" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="0">
-        <v>2</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="F7" s="0">
-        <v>6</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="H7" s="0">
-        <v>0</v>
-      </c>
-      <c r="I7" s="0">
+      <c r="L6">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="C7">
+        <v>11002</v>
+      </c>
+      <c r="D7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>0.2</v>
       </c>
-      <c r="J7" s="0">
+      <c r="K7" s="3">
         <v>0.2</v>
       </c>
-      <c r="K7" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="0">
-        <v>3</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8" s="0">
-        <v>0</v>
-      </c>
-      <c r="G8" s="0" t="s">
+      <c r="L7">
+        <v>11002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="C8">
+        <v>11003</v>
+      </c>
+      <c r="D8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>60</v>
+      </c>
+      <c r="H8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.1</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="L8">
+        <v>11003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="C9">
+        <v>11004</v>
+      </c>
+      <c r="D9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" t="s">
         <v>78</v>
       </c>
-      <c r="H8" s="0">
-        <v>0</v>
-      </c>
-      <c r="I8" s="0">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>40</v>
+      </c>
+      <c r="H9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.3</v>
+      </c>
+      <c r="K9" s="3">
         <v>0.2</v>
       </c>
-      <c r="J8" s="0">
+      <c r="L9">
+        <v>11004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="C10">
+        <v>12001</v>
+      </c>
+      <c r="D10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>30</v>
+      </c>
+      <c r="H10" t="s">
+        <v>88</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.1</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="L10">
+        <v>12001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="C11">
+        <v>12002</v>
+      </c>
+      <c r="D11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>25</v>
+      </c>
+      <c r="H11" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
         <v>0.2</v>
       </c>
-      <c r="K8" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="0">
-        <v>4</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="F9" s="0">
-        <v>0</v>
-      </c>
-      <c r="G9" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="H9" s="0">
-        <v>0</v>
-      </c>
-      <c r="I9" s="0">
+      <c r="K11" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="L11">
+        <v>12002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="C12">
+        <v>13001</v>
+      </c>
+      <c r="D12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>93</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
         <v>0.2</v>
       </c>
-      <c r="J9" s="0">
+      <c r="K12">
         <v>0.2</v>
       </c>
-      <c r="K9" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="0">
-        <v>5</v>
-      </c>
-      <c r="C10" s="0" t="s">
+      <c r="L12">
+        <v>13001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="C13">
+        <v>13002</v>
+      </c>
+      <c r="D13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>93</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.2</v>
+      </c>
+      <c r="K13">
+        <v>0.2</v>
+      </c>
+      <c r="L13">
+        <v>13002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="C14">
+        <v>13003</v>
+      </c>
+      <c r="D14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>93</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.2</v>
+      </c>
+      <c r="K14">
+        <v>0.2</v>
+      </c>
+      <c r="L14">
+        <v>13003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="C15">
+        <v>13004</v>
+      </c>
+      <c r="D15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.2</v>
+      </c>
+      <c r="K15">
+        <v>0.2</v>
+      </c>
+      <c r="L15">
+        <v>13004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="C16">
+        <v>13005</v>
+      </c>
+      <c r="D16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" t="s">
         <v>81</v>
       </c>
-      <c r="D10" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" s="0">
-        <v>2</v>
-      </c>
-      <c r="F10" s="0">
-        <v>0</v>
-      </c>
-      <c r="G10" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="H10" s="0">
-        <v>0</v>
-      </c>
-      <c r="I10" s="0">
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>55</v>
+      </c>
+      <c r="H16" t="s">
+        <v>84</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.1</v>
+      </c>
+      <c r="K16">
         <v>0.2</v>
       </c>
-      <c r="J10" s="0">
-        <v>0.2</v>
-      </c>
-      <c r="K10" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="0">
-        <v>6</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" s="0">
-        <v>2</v>
-      </c>
-      <c r="F11" s="0">
-        <v>0</v>
-      </c>
-      <c r="G11" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="H11" s="0">
-        <v>0</v>
-      </c>
-      <c r="I11" s="0">
-        <v>0.2</v>
-      </c>
-      <c r="J11" s="0">
-        <v>0.2</v>
-      </c>
-      <c r="K11" s="3">
-        <v>3</v>
+      <c r="L16">
+        <v>13005</v>
       </c>
     </row>
   </sheetData>
@@ -2279,16 +2633,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to AION.CoreGame under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
-For more information about EPPlus, see https://epplussoftware.com/
-
 </file>
--- a/Configs/GameConfig/Datas/局内.xlsx
+++ b/Configs/GameConfig/Datas/局内.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="基础建筑表" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="103">
   <si>
     <t>##var</t>
   </si>
@@ -212,6 +212,9 @@
     <t>debuff_duration</t>
   </si>
   <si>
+    <t>damageRange</t>
+  </si>
+  <si>
     <t>speed</t>
   </si>
   <si>
@@ -221,6 +224,9 @@
     <t>buffs</t>
   </si>
   <si>
+    <t>spawnUnit</t>
+  </si>
+  <si>
     <t>pre_cast_anim_time</t>
   </si>
   <si>
@@ -233,7 +239,10 @@
     <t>CDamageEffect#sep=,</t>
   </si>
   <si>
-    <t>int#ref=battle.TbBuff</t>
+    <t>(list#sep=;),battle.BuffConfig</t>
+  </si>
+  <si>
+    <t>int#ref=battle.TbUnit</t>
   </si>
   <si>
     <t>子弹id</t>
@@ -248,19 +257,25 @@
     <t>持续时间</t>
   </si>
   <si>
+    <t>伤害范围</t>
+  </si>
+  <si>
     <t>飞行速度</t>
   </si>
   <si>
     <t>施加buff</t>
   </si>
   <si>
+    <t>生成单位</t>
+  </si>
+  <si>
     <t>前摇动画间隔</t>
   </si>
   <si>
     <t>后摇动画间隔</t>
   </si>
   <si>
-    <t>预制体路径</t>
+    <t>子弹预制体路径</t>
   </si>
   <si>
     <t>战士普攻</t>
@@ -2126,23 +2141,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="49.3636363636364" customWidth="1"/>
     <col min="3" max="3" width="31.6363636363636" customWidth="1"/>
     <col min="4" max="4" width="38.5454545454545" customWidth="1"/>
     <col min="5" max="5" width="15.5" customWidth="1"/>
-    <col min="6" max="6" width="22.7818181818182" customWidth="1"/>
-    <col min="7" max="7" width="19.7818181818182" customWidth="1"/>
-    <col min="8" max="8" width="17.9636363636364" customWidth="1"/>
-    <col min="9" max="9" width="29.7272727272727" customWidth="1"/>
-    <col min="10" max="10" width="17.9636363636364" customWidth="1"/>
-    <col min="11" max="11" width="33.2727272727273" customWidth="1"/>
-    <col min="12" max="12" width="49.6181818181818" customWidth="1"/>
+    <col min="6" max="7" width="22.7818181818182" customWidth="1"/>
+    <col min="8" max="8" width="19.7818181818182" customWidth="1"/>
+    <col min="9" max="9" width="26.4090909090909" customWidth="1"/>
+    <col min="10" max="10" width="39.0363636363636" customWidth="1"/>
+    <col min="11" max="11" width="44.8090909090909" customWidth="1"/>
+    <col min="12" max="12" width="20.7454545454545" customWidth="1"/>
+    <col min="13" max="13" width="33.2727272727273" customWidth="1"/>
+    <col min="14" max="14" width="49.6181818181818" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2173,23 +2189,29 @@
       <c r="J1" t="s">
         <v>63</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>64</v>
       </c>
       <c r="L1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="N1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="2"/>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2203,7 +2225,7 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -2212,33 +2234,39 @@
         <v>12</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J3" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L3" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L3" t="s">
+      <c r="N3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -2246,383 +2274,403 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H5"/>
-      <c r="I5" t="s">
-        <v>73</v>
+        <v>75</v>
+      </c>
+      <c r="H5" t="s">
+        <v>76</v>
       </c>
       <c r="J5" t="s">
-        <v>74</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
+      </c>
+      <c r="K5" t="s">
+        <v>78</v>
       </c>
       <c r="L5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>79</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="N5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="C6">
         <v>11001</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
         <v>45</v>
       </c>
-      <c r="H6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
+      <c r="I6" t="s">
+        <v>84</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
         <v>0.1</v>
       </c>
-      <c r="K6" s="3">
+      <c r="M6" s="3">
         <v>0.2</v>
       </c>
-      <c r="L6">
+      <c r="N6">
         <v>11001</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:14">
       <c r="C7">
         <v>11002</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
         <v>45</v>
       </c>
-      <c r="H7" t="s">
-        <v>82</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
+      <c r="I7" t="s">
+        <v>87</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
         <v>0.2</v>
       </c>
-      <c r="K7" s="3">
+      <c r="M7" s="3">
         <v>0.2</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>11002</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:14">
       <c r="C8">
         <v>11003</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
         <v>60</v>
       </c>
-      <c r="H8" t="s">
-        <v>84</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
+      <c r="I8" t="s">
+        <v>89</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
         <v>0.1</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>0.2</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>11003</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:14">
       <c r="C9">
         <v>11004</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
         <v>40</v>
       </c>
-      <c r="H9" t="s">
-        <v>86</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
+      <c r="I9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
         <v>0.3</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>0.2</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>11004</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:14">
       <c r="C10">
         <v>12001</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
         <v>30</v>
       </c>
-      <c r="H10" t="s">
-        <v>88</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
+      <c r="I10" t="s">
+        <v>93</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
         <v>0.1</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>0.1</v>
       </c>
-      <c r="L10">
-        <v>12001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+    </row>
+    <row r="11" spans="1:14">
       <c r="C11">
         <v>12002</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
         <v>25</v>
       </c>
-      <c r="H11" t="s">
-        <v>90</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
+      <c r="I11" t="s">
+        <v>95</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
         <v>0.2</v>
       </c>
-      <c r="K11" s="3">
+      <c r="M11" s="3">
         <v>0.3</v>
       </c>
-      <c r="L11">
-        <v>12002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+    </row>
+    <row r="12" spans="1:14">
       <c r="C12">
         <v>13001</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12" t="s">
-        <v>93</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>98</v>
+      </c>
+      <c r="K12">
+        <v>1002</v>
+      </c>
+      <c r="L12">
         <v>0.2</v>
       </c>
-      <c r="K12">
+      <c r="M12">
         <v>0.2</v>
       </c>
-      <c r="L12">
-        <v>13001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+    </row>
+    <row r="13" spans="1:14">
       <c r="C13">
         <v>13002</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E13" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13" t="s">
-        <v>93</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" t="s">
+        <v>98</v>
+      </c>
+      <c r="K13">
+        <v>1001</v>
+      </c>
+      <c r="L13">
         <v>0.2</v>
       </c>
-      <c r="K13">
+      <c r="M13">
         <v>0.2</v>
       </c>
-      <c r="L13">
-        <v>13002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+    </row>
+    <row r="14" spans="1:14">
       <c r="C14">
         <v>13003</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14" t="s">
-        <v>93</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14">
+        <v>1004</v>
+      </c>
+      <c r="L14">
         <v>0.2</v>
       </c>
-      <c r="K14">
+      <c r="M14">
         <v>0.2</v>
       </c>
-      <c r="L14">
-        <v>13003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+    </row>
+    <row r="15" spans="1:14">
       <c r="C15">
         <v>13004</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E15" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15" t="s">
-        <v>93</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" t="s">
+        <v>98</v>
+      </c>
+      <c r="K15">
+        <v>1003</v>
+      </c>
+      <c r="L15">
         <v>0.2</v>
       </c>
-      <c r="K15">
+      <c r="M15">
         <v>0.2</v>
       </c>
-      <c r="L15">
-        <v>13004</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+    </row>
+    <row r="16" spans="1:14">
       <c r="C16">
         <v>13005</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
         <v>55</v>
       </c>
-      <c r="H16" t="s">
-        <v>84</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
+      <c r="I16" t="s">
+        <v>89</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
         <v>0.1</v>
       </c>
-      <c r="K16">
+      <c r="M16">
         <v>0.2</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>13005</v>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/局内.xlsx
+++ b/Configs/GameConfig/Datas/局内.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="基础建筑表" sheetId="1" r:id="rId1"/>
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H6" s="8">
         <v>3001</v>
@@ -1630,7 +1630,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H7" s="8">
         <v>3002</v>
@@ -1655,7 +1655,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H8" s="8">
         <v>3003</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H9" s="8">
         <v>3004</v>
@@ -1705,7 +1705,7 @@
         <v>6</v>
       </c>
       <c r="G10" s="8">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="H10" s="8">
         <v>3005</v>
